--- a/data/trans_camb/IP08-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP08-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-9.732445333589117</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-3.823869553160371</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-7.444371199057827</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.545123327633739</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-8.623198967814345</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-3.193734597337576</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-14.44880220979291</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-10.1118727031395</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-12.09658565300706</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.657989168424654</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-11.59813260903093</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-7.927504985560168</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-5.54226002484045</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.269259678565472</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-2.760410114972539</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.752487876209016</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-5.476069027937171</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.865148260031465</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.6033114221374093</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.2370405483011695</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.5161959582257221</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1764799658400713</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.5636586654956901</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2087596711848793</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.7511752239526517</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5696604029503354</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.6976378511816673</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.5363431941020007</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6782089507056696</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4685682295651432</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>-0.3950155563001201</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.3158110781831916</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-0.2142083212234802</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.3890531834649665</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.396101479061576</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1626745363309827</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-10.64198533354609</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.05790345123057039</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3958454992509824</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.407337369208146</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-5.532794544254095</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.4527093416285211</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-15.65122065537506</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.155023927479706</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.895477476471122</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.023337877669988</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-8.713367782796338</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-4.617059043953265</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>-5.896934708000071</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>15.1909655488581</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.413193586059839</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.03048250971249</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-1.761405132980739</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>6.415734854679569</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.6409100110092091</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.003487216003641127</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.04026480769806987</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1431522365283857</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.4184290888311022</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.03423708504044729</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.793470272745578</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.3470562670311055</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.4015650028729098</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.5046223639662777</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5860345896011017</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3169690629304246</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>-0.4090144494048504</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.034698100541694</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.5872618514872782</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.3969297932890575</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.1520488238246173</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5857968872811218</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>3.619998990819253</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4.783174221789682</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-5.084225784932422</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.8300180203273846</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.7348261114466805</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2.056715746996857</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-0.9726431587744919</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.3084613122099739</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-9.678698914717884</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.997764064016149</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-3.887793346106086</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.556274905501558</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>8.307195283072771</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.672651260722825</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.1119812075185333</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.216162676551855</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.96312831484504</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5.553986905683412</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.6350600790466954</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.8391170845869274</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.4855471243607068</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.07926730243410797</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.09131070039494679</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.2555708792136819</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.1805317810045591</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.037500814898973</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.7311228196370309</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.4655262397444029</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.4094029731302862</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.1572931447625152</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>2.208936779347951</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2.629196684217851</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.03455701531764812</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.5734405175820395</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.5089640558791493</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.9311020163506206</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-7.961646211675361</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-3.384005908318072</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-7.560164423799288</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.177292384269763</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-7.713569447838318</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-1.818903719054948</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-16.06400905551238</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-10.81162041270136</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-14.87681467421713</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-7.70622182827116</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-12.47392343068256</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-6.573914906147252</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>-1.514692175315296</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.968412255301078</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-2.024002985268457</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>6.216273912418909</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-2.682541486047763</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>3.139606886332705</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.5454618486338951</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.2318422684786416</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.7677567475631507</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.01800455872178836</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.6197262149950646</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.1461349800339539</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.8089771065598431</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.5741076870934427</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.9413305566638123</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.5209589472091563</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.8029777870459509</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.4335774534549946</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>-0.07712349568313687</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.378266357271148</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>-0.1658367575941102</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1.083312383657283</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-0.2612268925022499</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.3498063753589328</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-6.902753644683182</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-1.016475190456898</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-4.774800269205966</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1.895464055112521</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-5.864728049262602</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-1.38774044257271</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-9.638492311543869</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-4.158572824541555</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-7.260695500282016</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-4.473428448358625</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-7.658838125950977</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-3.605030180120757</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-4.268904764759555</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.556024217544133</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-1.989028105553905</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1.199444790399243</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-4.099768293296849</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.216902225039767</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.5000552832072211</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.07363637982771544</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.4128148940559795</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.1638761307241687</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.4613246830421766</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.1091608876723892</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.6228552208706652</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.280837305803149</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.5643399000879078</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.3536671163933144</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.5624330976993767</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.2647389711343672</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.343434089391412</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.2708458107993432</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.2009219469770624</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.1134079227552689</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.3531704883455761</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.1049814707299304</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
